--- a/data/trans_dic/IP12-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP12-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que limitaron su actividad por dolores o síntomas</t>
+          <t>Menores que limitaron su actividad por dolores o síntomas (tasa de respuesta: 99,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,98; 11,9</t>
+          <t>2,64; 11,85</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,27; 16,38</t>
+          <t>6,59; 17,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,89; 19,66</t>
+          <t>5,46; 19,4</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,49; 14,92</t>
+          <t>2,21; 13,26</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,16; 11,97</t>
+          <t>3,07; 11,86</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,23; 14,24</t>
+          <t>4,22; 15,07</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,98; 9,64</t>
+          <t>0,95; 9,11</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,69; 20,3</t>
+          <t>5,69; 20,15</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,88; 10,18</t>
+          <t>3,79; 9,57</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6,42; 13,75</t>
+          <t>6,36; 13,76</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3,8; 11,77</t>
+          <t>4,08; 10,98</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,23; 15,04</t>
+          <t>4,94; 14,43</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,07; 9,16</t>
+          <t>5,39; 9,24</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,83; 10,23</t>
+          <t>5,83; 9,8</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,16; 8,91</t>
+          <t>5,3; 8,96</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,19; 9,23</t>
+          <t>5,02; 9,05</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,15; 8,69</t>
+          <t>5,13; 8,89</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,05; 11,42</t>
+          <t>7,25; 11,75</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,79; 9,64</t>
+          <t>5,59; 9,46</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,58; 9,96</t>
+          <t>5,52; 9,89</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,58; 8,21</t>
+          <t>5,63; 8,34</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7,05; 10,1</t>
+          <t>6,93; 10,06</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5,88; 8,55</t>
+          <t>5,97; 8,63</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,78; 8,72</t>
+          <t>5,81; 8,73</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,81; 8,0</t>
+          <t>2,62; 7,76</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,5; 14,2</t>
+          <t>6,23; 14,13</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,37; 13,91</t>
+          <t>6,44; 13,55</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,8; 12,19</t>
+          <t>4,91; 11,84</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,68; 10,06</t>
+          <t>3,72; 9,99</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,79; 10,66</t>
+          <t>3,79; 11,03</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,03; 8,75</t>
+          <t>2,82; 8,52</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,26; 11,85</t>
+          <t>4,53; 12,08</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,83; 7,87</t>
+          <t>3,93; 7,82</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5,73; 10,97</t>
+          <t>5,83; 10,78</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5,36; 10,0</t>
+          <t>5,27; 10,04</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,4; 10,64</t>
+          <t>5,29; 10,65</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,04; 8,15</t>
+          <t>5,03; 8,08</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,04; 10,37</t>
+          <t>7,05; 10,49</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,25; 9,63</t>
+          <t>6,33; 9,62</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,43; 8,87</t>
+          <t>5,49; 8,98</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,3; 8,34</t>
+          <t>5,15; 7,98</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,85; 10,38</t>
+          <t>6,88; 10,37</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,06; 8,05</t>
+          <t>5,21; 8,19</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,08; 9,74</t>
+          <t>6,25; 9,82</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,56; 7,6</t>
+          <t>5,5; 7,58</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7,44; 9,91</t>
+          <t>7,36; 9,79</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6,07; 8,36</t>
+          <t>6,23; 8,39</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6,25; 8,85</t>
+          <t>6,27; 8,9</t>
         </is>
       </c>
     </row>
@@ -1215,4 +1216,995 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que limitaron su actividad por dolores o síntomas (tasa de respuesta: 99,99%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>5653</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>10061</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>6580</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>3560</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>5504</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>7048</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>2239</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>6831</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>11157</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>17109</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>8819</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>10391</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>2397; 10763</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>6086; 15704</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>3244; 11519</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1208; 7253</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>2665; 10296</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>3640; 12987</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>654; 6251</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>3531; 12495</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>6739; 17003</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>11358; 24572</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>5217; 14055</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>5761; 16834</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>29627</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>35049</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>32420</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>32015</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>32033</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>45295</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>36370</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>38702</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>61660</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>80344</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>68790</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>70717</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>22420; 38453</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>26378; 44339</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>25020; 42281</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>23071; 41612</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>24469; 42402</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>35868; 58080</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>27324; 46257</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>28522; 51069</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>50245; 74489</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>65559; 95215</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>57376; 82886</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>56743; 85198</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>8597</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>16181</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>16726</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>11697</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>9856</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>11218</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>9873</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>13570</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>18453</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>27399</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>26599</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>25268</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>4566; 13509</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>10389; 23563</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>11126; 23410</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>7339; 17704</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>5889; 15800</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>6530; 19003</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>5281; 15968</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>8305; 22140</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>13064; 25970</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>19782; 36561</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>18969; 36154</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>17611; 35461</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>43878</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>61292</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>55726</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>47272</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>47392</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>63560</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>48482</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>59103</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>91270</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>124852</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>104208</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>106375</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>34289; 55048</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>50187; 74651</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>44576; 67704</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>36460; 59621</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>37181; 57591</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>51779; 78100</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>38826; 61026</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>47607; 74856</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>77124; 106296</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>107765; 143394</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>90269; 121541</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>89398; 126919</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP12-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP12-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que limitaron su actividad por dolores o síntomas (tasa de respuesta: 99,99%)</t>
+          <t>Menores que en las últimas 2 semanas limitaron su actividad por dolores o síntomas (tasa de respuesta: 99,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,64; 11,85</t>
+          <t>2,4; 11,71</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,59; 17,0</t>
+          <t>6,36; 16,69</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,46; 19,4</t>
+          <t>5,84; 19,93</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,21; 13,26</t>
+          <t>2,63; 14,92</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,07; 11,86</t>
+          <t>3,15; 12,2</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,22; 15,07</t>
+          <t>4,35; 14,46</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,95; 9,11</t>
+          <t>0,97; 8,68</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,69; 20,15</t>
+          <t>5,8; 20,44</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,79; 9,57</t>
+          <t>3,49; 9,68</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6,36; 13,76</t>
+          <t>6,38; 13,88</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4,08; 10,98</t>
+          <t>4,0; 11,48</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,94; 14,43</t>
+          <t>5,16; 14,12</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,39; 9,24</t>
+          <t>5,32; 9,27</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,83; 9,8</t>
+          <t>5,8; 9,93</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,3; 8,96</t>
+          <t>5,12; 9,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,02; 9,05</t>
+          <t>4,85; 9,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,13; 8,89</t>
+          <t>5,13; 8,69</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,25; 11,75</t>
+          <t>7,36; 11,62</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,59; 9,46</t>
+          <t>5,8; 9,79</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,52; 9,89</t>
+          <t>5,53; 9,87</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,63; 8,34</t>
+          <t>5,66; 8,36</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6,93; 10,06</t>
+          <t>7,03; 10,25</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5,97; 8,63</t>
+          <t>5,92; 8,45</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,81; 8,73</t>
+          <t>5,83; 8,9</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,62; 7,76</t>
+          <t>2,83; 7,96</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,23; 14,13</t>
+          <t>6,37; 14,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,44; 13,55</t>
+          <t>6,33; 14,26</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,91; 11,84</t>
+          <t>5,08; 12,32</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,72; 9,99</t>
+          <t>3,74; 9,67</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,79; 11,03</t>
+          <t>3,94; 10,97</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,82; 8,52</t>
+          <t>2,96; 8,73</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,53; 12,08</t>
+          <t>4,31; 11,79</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,93; 7,82</t>
+          <t>3,79; 7,77</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5,83; 10,78</t>
+          <t>5,76; 10,75</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5,27; 10,04</t>
+          <t>5,32; 9,93</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,29; 10,65</t>
+          <t>5,4; 10,29</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,03; 8,08</t>
+          <t>5,05; 8,16</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,05; 10,49</t>
+          <t>6,95; 10,52</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,33; 9,62</t>
+          <t>6,34; 9,67</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,49; 8,98</t>
+          <t>5,59; 8,9</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,15; 7,98</t>
+          <t>5,33; 8,29</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,88; 10,37</t>
+          <t>6,91; 10,12</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,21; 8,19</t>
+          <t>5,14; 8,1</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,25; 9,82</t>
+          <t>6,02; 9,55</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,5; 7,58</t>
+          <t>5,49; 7,59</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7,36; 9,79</t>
+          <t>7,38; 10,03</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6,23; 8,39</t>
+          <t>6,15; 8,38</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6,27; 8,9</t>
+          <t>6,26; 8,74</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que limitaron su actividad por dolores o síntomas (tasa de respuesta: 99,99%)</t>
+          <t>Menores que en las últimas 2 semanas limitaron su actividad por dolores o síntomas (tasa de respuesta: 99,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2397; 10763</t>
+          <t>2182; 10636</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6086; 15704</t>
+          <t>5873; 15414</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3244; 11519</t>
+          <t>3469; 11832</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1208; 7253</t>
+          <t>1435; 8160</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2665; 10296</t>
+          <t>2739; 10597</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3640; 12987</t>
+          <t>3746; 12461</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>654; 6251</t>
+          <t>666; 5954</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3531; 12495</t>
+          <t>3594; 12671</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>6739; 17003</t>
+          <t>6201; 17207</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>11358; 24572</t>
+          <t>11398; 24779</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5217; 14055</t>
+          <t>5126; 14696</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5761; 16834</t>
+          <t>6016; 16474</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>22420; 38453</t>
+          <t>22132; 38585</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>26378; 44339</t>
+          <t>26245; 44907</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>25020; 42281</t>
+          <t>24164; 42471</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>23071; 41612</t>
+          <t>22287; 41373</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>24469; 42402</t>
+          <t>24467; 41453</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>35868; 58080</t>
+          <t>36393; 57446</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>27324; 46257</t>
+          <t>28364; 47827</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>28522; 51069</t>
+          <t>28563; 50975</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>50245; 74489</t>
+          <t>50541; 74675</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>65559; 95215</t>
+          <t>66566; 97074</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>57376; 82886</t>
+          <t>56884; 81122</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>56743; 85198</t>
+          <t>56942; 86881</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4566; 13509</t>
+          <t>4923; 13849</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>10389; 23563</t>
+          <t>10620; 23358</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11126; 23410</t>
+          <t>10925; 24629</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7339; 17704</t>
+          <t>7602; 18423</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>5889; 15800</t>
+          <t>5915; 15298</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6530; 19003</t>
+          <t>6793; 18890</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5281; 15968</t>
+          <t>5545; 16364</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>8305; 22140</t>
+          <t>7895; 21623</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>13064; 25970</t>
+          <t>12598; 25803</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>19782; 36561</t>
+          <t>19526; 36455</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>18969; 36154</t>
+          <t>19150; 35768</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>17611; 35461</t>
+          <t>17980; 34242</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>34289; 55048</t>
+          <t>34365; 55556</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>50187; 74651</t>
+          <t>49428; 74848</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>44576; 67704</t>
+          <t>44619; 68026</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>36460; 59621</t>
+          <t>37102; 59086</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>37181; 57591</t>
+          <t>38468; 59830</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>51779; 78100</t>
+          <t>52058; 76160</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>38826; 61026</t>
+          <t>38294; 60359</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>47607; 74856</t>
+          <t>45885; 72733</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>77124; 106296</t>
+          <t>76992; 106453</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>107765; 143394</t>
+          <t>107994; 146824</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>90269; 121541</t>
+          <t>89092; 121457</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>89398; 126919</t>
+          <t>89319; 124694</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP12-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP12-Estudios-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>6,34%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>8,18%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3,26%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>11,68%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>6,22%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>10,89%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>11,08%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>6,51%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>6,34%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>8,18%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>3,26%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>9,61%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,4; 11,71</t>
+          <t>3,16; 11,97</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,36; 16,69</t>
+          <t>4,23; 14,24</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,84; 19,93</t>
+          <t>0,98; 9,64</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,63; 14,92</t>
+          <t>5,99; 21,84</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,15; 12,2</t>
+          <t>2,98; 11,9</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,35; 14,46</t>
+          <t>6,27; 16,38</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,97; 8,68</t>
+          <t>5,89; 19,66</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,8; 20,44</t>
+          <t>2,63; 15,84</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,49; 9,68</t>
+          <t>3,88; 10,18</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6,38; 13,88</t>
+          <t>6,42; 13,75</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4,0; 11,48</t>
+          <t>3,8; 11,77</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,16; 14,12</t>
+          <t>5,73; 15,89</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>6,72%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>9,16%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>7,44%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>7,63%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>7,12%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>7,75%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>6,87%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>6,96%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>6,72%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>9,16%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>7,44%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,46%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,32; 9,27</t>
+          <t>5,15; 8,69</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,8; 9,93</t>
+          <t>7,05; 11,42</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,12; 9,0</t>
+          <t>5,79; 9,64</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,85; 9,0</t>
+          <t>5,74; 10,43</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,13; 8,69</t>
+          <t>5,07; 9,16</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,36; 11,62</t>
+          <t>5,83; 10,23</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,8; 9,79</t>
+          <t>5,16; 8,91</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,53; 9,87</t>
+          <t>5,48; 9,48</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,66; 8,36</t>
+          <t>5,58; 8,21</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7,03; 10,25</t>
+          <t>7,05; 10,1</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5,92; 8,45</t>
+          <t>5,88; 8,55</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,83; 8,9</t>
+          <t>6,07; 8,95</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>6,23%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>6,51%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>5,27%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>7,41%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>4,94%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>9,7%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>9,68%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>7,82%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>6,23%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>6,51%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>5,27%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,67%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,83; 7,96</t>
+          <t>3,68; 10,06</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,37; 14,0</t>
+          <t>3,79; 10,66</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,33; 14,26</t>
+          <t>3,03; 8,75</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,08; 12,32</t>
+          <t>4,15; 12,07</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,74; 9,67</t>
+          <t>2,81; 8,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,94; 10,97</t>
+          <t>6,5; 14,2</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,96; 8,73</t>
+          <t>6,37; 13,91</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,31; 11,79</t>
+          <t>4,88; 12,31</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,79; 7,77</t>
+          <t>3,83; 7,87</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5,76; 10,75</t>
+          <t>5,73; 10,97</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5,32; 9,93</t>
+          <t>5,36; 10,0</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,4; 10,29</t>
+          <t>5,46; 10,79</t>
         </is>
       </c>
     </row>
@@ -1069,49 +1069,49 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>6,56%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>8,44%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>6,51%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>7,91%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>6,44%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>8,62%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>7,92%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>7,12%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>6,56%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>8,44%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>7,42%</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>6,51%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>7,76%</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>6,51%</t>
-        </is>
-      </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
           <t>8,53%</t>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,68%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,05; 8,16</t>
+          <t>5,3; 8,34</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,95; 10,52</t>
+          <t>6,85; 10,38</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,34; 9,67</t>
+          <t>5,06; 8,05</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,59; 8,9</t>
+          <t>6,23; 10,0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,33; 8,29</t>
+          <t>5,04; 8,15</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,91; 10,12</t>
+          <t>7,04; 10,37</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,14; 8,1</t>
+          <t>6,25; 9,63</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,02; 9,55</t>
+          <t>5,67; 9,22</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,49; 7,59</t>
+          <t>5,56; 7,6</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7,38; 10,03</t>
+          <t>7,44; 9,91</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6,15; 8,38</t>
+          <t>6,07; 8,36</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6,26; 8,74</t>
+          <t>6,44; 9,11</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1260,7 +1260,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1373,37 +1373,37 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1436,42 +1436,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>5504</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>7048</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2239</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>6625</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>5653</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>10061</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>6580</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>3560</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>5504</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>7048</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>2239</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6831</t>
+          <t>3317</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>10391</t>
+          <t>9942</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2182; 10636</t>
+          <t>2747; 10399</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5873; 15414</t>
+          <t>3644; 12272</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3469; 11832</t>
+          <t>671; 6615</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1435; 8160</t>
+          <t>3399; 12392</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2739; 10597</t>
+          <t>2710; 10815</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3746; 12461</t>
+          <t>5795; 15128</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>666; 5954</t>
+          <t>3496; 11673</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3594; 12671</t>
+          <t>1229; 7408</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>6201; 17207</t>
+          <t>6898; 18085</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>11398; 24779</t>
+          <t>11466; 24544</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5126; 14696</t>
+          <t>4861; 15065</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6016; 16474</t>
+          <t>5933; 16449</t>
         </is>
       </c>
     </row>
@@ -1576,42 +1576,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>52</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1644,42 +1644,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>32033</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>45295</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>36370</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>36302</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>29627</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>35049</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>32420</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>32015</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>32033</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>45295</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>36370</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>38702</t>
+          <t>31381</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>70717</t>
+          <t>67683</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>22132; 38585</t>
+          <t>24565; 41467</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>26245; 44907</t>
+          <t>34883; 56452</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>24164; 42471</t>
+          <t>28286; 47115</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>22287; 41373</t>
+          <t>27282; 49617</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>24467; 41453</t>
+          <t>21106; 38107</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>36393; 57446</t>
+          <t>26345; 46247</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>28364; 47827</t>
+          <t>24324; 42024</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>28563; 50975</t>
+          <t>23645; 40913</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>50541; 74675</t>
+          <t>49816; 73349</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>66566; 97074</t>
+          <t>66715; 95633</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>56884; 81122</t>
+          <t>56454; 82124</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>56942; 86881</t>
+          <t>55059; 81198</t>
         </is>
       </c>
     </row>
@@ -1784,42 +1784,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>19</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1852,42 +1852,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>9856</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>11218</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>9873</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>12477</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>8597</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>16181</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>16726</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>11697</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>9856</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>11218</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>9873</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>13570</t>
+          <t>11950</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>25268</t>
+          <t>24427</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4923; 13849</t>
+          <t>5824; 15909</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>10620; 23358</t>
+          <t>6534; 18367</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10925; 24629</t>
+          <t>5679; 16400</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7602; 18423</t>
+          <t>6988; 20328</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>5915; 15298</t>
+          <t>4883; 13926</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6793; 18890</t>
+          <t>10842; 23689</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5545; 16364</t>
+          <t>11002; 24019</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>7895; 21623</t>
+          <t>7321; 18463</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>12598; 25803</t>
+          <t>12733; 26146</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>19526; 36455</t>
+          <t>19419; 37181</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>19150; 35768</t>
+          <t>19318; 36008</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>17980; 34242</t>
+          <t>17392; 34352</t>
         </is>
       </c>
     </row>
@@ -1992,42 +1992,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>88</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>85</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>77</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2060,42 +2060,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>47392</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>63560</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>48482</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>55404</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>43878</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>61292</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>55726</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>47272</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>47392</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>63560</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>48482</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>59103</t>
+          <t>46649</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>106375</t>
+          <t>102053</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>34365; 55556</t>
+          <t>38238; 60195</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>49428; 74848</t>
+          <t>51571; 78151</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>44619; 68026</t>
+          <t>37665; 59976</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>37102; 59086</t>
+          <t>43666; 70112</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>38468; 59830</t>
+          <t>34308; 55512</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>52058; 76160</t>
+          <t>50093; 73802</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>38294; 60359</t>
+          <t>43970; 67739</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>45885; 72733</t>
+          <t>35618; 57963</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>76992; 106453</t>
+          <t>77948; 106589</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>107994; 146824</t>
+          <t>108873; 145132</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>89092; 121457</t>
+          <t>87932; 121156</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>89319; 124694</t>
+          <t>85554; 121135</t>
         </is>
       </c>
     </row>
